--- a/_docs_/trim4/Formato_QA_Profesional_SENA(Recuperado automáticamente) (1).xlsx
+++ b/_docs_/trim4/Formato_QA_Profesional_SENA(Recuperado automáticamente) (1).xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="384">
   <si>
     <t>ID</t>
   </si>
@@ -487,16 +487,21 @@
 advertencia.</t>
   </si>
   <si>
-    <t>p</t>
-  </si>
-  <si>
-    <t>Actualiza los datos del ususario</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Actualizo los datos del ususario </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 11/06/2026</t>
+    <t>Kevin/Alejandro/Hernandez/Perez/Kevincito03@gmail.com/123456/32343539/Beneficiario/Activo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.Iniciar sesión como administrador.
+2.Ingresar al apartado de usuarios.
+3.Dar clic en el lápiz en la columna acciones.
+4. Actualizar la información del usuario.
+5.Dar clic en guardar en el botón rojo.
+</t>
+  </si>
+  <si>
+    <t>Actualizar los datos del ususario con os datos exactos que se necesiten.</t>
+  </si>
+  <si>
+    <t>Actualizo los datos del ususario de manera correcta despues de dar al boton guardar.</t>
   </si>
   <si>
     <t>TC-003</t>
@@ -515,10 +520,20 @@
 advertencia.</t>
   </si>
   <si>
-    <t>Eliminacion del usuario</t>
-  </si>
-  <si>
-    <t>Se elimina el usuario</t>
+    <t>Se elimino la cuenta de cristian .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.Iniciar sesión como administrador.
+2.Ingresar al apartado de usuarios.
+3.Dar clic en la basurita que está en la columna acciones.
+4. Dar clic en confirmar en el botón rojo .
+</t>
+  </si>
+  <si>
+    <t>Eliminación del usuario después de escogerlo y confirmar en el botón rojo para que así se haga el proceso de eliminación.</t>
+  </si>
+  <si>
+    <t>Se elimina el usuario y no se ve mas en la interfaz.</t>
   </si>
   <si>
     <t>TC-004</t>
@@ -535,7 +550,16 @@
 Debe existir autenticación válida.</t>
   </si>
   <si>
-    <t>Consultar al ususario requerido</t>
+    <t>En el buscador se consulto al usuario juan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.Iniciar sesión como administrador.
+2.Ingresar al apartado de usuarios.
+3.Ingresar el nombre del usuario a consultar en el buscador.
+</t>
+  </si>
+  <si>
+    <t>Consultar al usuario requerido por medio del buscador que se encuentra en la sección de  usuarios ingresando como administrador en la parte superior de los usuarios.</t>
   </si>
   <si>
     <t>Muestra el ususario consultado</t>
@@ -553,20 +577,26 @@
 Se respetan permisos del sistema.</t>
   </si>
   <si>
-    <t xml:space="preserve">Consultar los usuarios requeridos </t>
-  </si>
-  <si>
-    <t>Muestra los ususarios consultados</t>
-  </si>
-  <si>
-    <t>11/06 2026</t>
+    <t>No se requiere</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.Iniciar sesión como administrador.
+2.Ingresar al apartado de usuarios.
+3.Se ve de entrada a todos los usuarios.
+</t>
+  </si>
+  <si>
+    <t>Mostrar todos los usuarios en pantalla simplemente ingresando al apartado de usuarios iniciando sesión como administrador.</t>
+  </si>
+  <si>
+    <t>Muestra todos los  ususarios en pantalla</t>
   </si>
   <si>
     <t>TC-006</t>
   </si>
   <si>
     <t>Asociará el evento a la organización o administrador
-creador y mostrará confirmación de creación exitosa.</t>
+creador y mostrará confirmación.</t>
   </si>
   <si>
     <t>El usuario debe tener sesión iniciada.
@@ -588,10 +618,10 @@
 </t>
   </si>
   <si>
-    <t>Mostrar en pantalla el recuadro con la información del evento, con la información que se inserta anteriormente .</t>
-  </si>
-  <si>
-    <t>El evento se crea efectivamente en el recuadro y mostrando la información que se dio.)</t>
+    <t>Mostrar en pantalla la fila con la información del evento, con la información que se inserta anteriormente .</t>
+  </si>
+  <si>
+    <t>El evento se crea efectivamente en la fila y muestra la información que se dio.</t>
   </si>
   <si>
     <t>Zharick</t>
@@ -612,16 +642,27 @@
 Los cambios deben respetar formatos válidos.</t>
   </si>
   <si>
-    <t>El cuadro de evento actualizara su informacion.</t>
-  </si>
-  <si>
-    <t>El cuadro que tiene la informacion se actualizo.</t>
+    <t>Tutoria para la gente mayor/Caritas Local/Educacion/20-07-2026/Activo -Abierto/Buscamos voluntarios para impartir clases de apoyo los fines de semana personas de la tercera edad.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.Iniciar sesión como administrador.
+2.Ingresar al apartado de eventos.
+3.Se ve de entrada a todos los usuarios.
+4.Actualizar la información del evento.
+5 Dar clic en guardar evento en el botón.
+</t>
+  </si>
+  <si>
+    <t>La fila de evento actualizara su informacion.</t>
+  </si>
+  <si>
+    <t>La fila que tiene la informacion se actualizo.</t>
   </si>
   <si>
     <t>TC-008</t>
   </si>
   <si>
-    <t>Mostrará notificación de eliminación exitosa.</t>
+    <t>No se evidencia el evento en la pantalla.</t>
   </si>
   <si>
     <t>El usuario debe tener permisos sobre el evento.
@@ -631,6 +672,16 @@
 Debe existir sesión iniciada.</t>
   </si>
   <si>
+    <t>Se elimino el evento Tutoria para la gente mayor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.Iniciar sesión como administrador.
+2.Ingresar al apartado de eventos.
+3.Vamos a la columna acciones y le damos a la basurita roja.
+4.Dar clic en el botón rojo que dice confirmar.
+</t>
+  </si>
+  <si>
     <t>Ver que el evento se ha eliminado.</t>
   </si>
   <si>
@@ -649,6 +700,15 @@
 Se deben respetar permisos de visibilidad.</t>
   </si>
   <si>
+    <t>En el buscador se consulto  el evento Campaña Sanitaria Comunitaria .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.Iniciar sesión como administrador.
+2.Ingresar al apartado de eventos.
+3.Ingresamos en el buscador el nombre del evento.
+</t>
+  </si>
+  <si>
     <t>Mostrara el evento seleccionado.</t>
   </si>
   <si>
@@ -670,10 +730,19 @@
 Se respetan permisos.</t>
   </si>
   <si>
+    <t xml:space="preserve">1.Iniciar sesión como administrador.
+2.Ingresar al apartado de eventos.
+3.Vemos todos los usuarios en pantalla.
+</t>
+  </si>
+  <si>
     <t>Los eventos consultados se mostraran en pantalla.</t>
   </si>
   <si>
     <t>Los eventos se muestran en pantalla.</t>
+  </si>
+  <si>
+    <t>p</t>
   </si>
   <si>
     <t>TC-011</t>
@@ -695,9 +764,6 @@
     <t>El reporte se envia para que el admi lo vea.</t>
   </si>
   <si>
-    <t>El reporte se envia correctamente.</t>
-  </si>
-  <si>
     <t>Kevin</t>
   </si>
   <si>
@@ -716,16 +782,10 @@
     <t>Muestra el reporte seleccionado.</t>
   </si>
   <si>
-    <t>Muestra en pantalla el reporte.</t>
-  </si>
-  <si>
     <t>TC-013</t>
   </si>
   <si>
     <t>Los reportes deben verse en pantalla.</t>
-  </si>
-  <si>
-    <t>Los reportes buscados se ven en la pantalla.</t>
   </si>
   <si>
     <t>TC-014</t>
@@ -763,17 +823,13 @@
     <t>El reporte se eliminara y no se vera.</t>
   </si>
   <si>
-    <t>El reporte ya no se ve en pantaya al confirmar.</t>
-  </si>
-  <si>
     <t>Nicolay</t>
   </si>
   <si>
     <t>TC-016</t>
   </si>
   <si>
-    <t>Permite registrar una donación en el sistema, asociándola
-a un evento u organización, garantizando control,
+    <t>Permite registrar una donación en el sistema, garantizando control,
 trazabilidad y almacenamiento seguro de la información.</t>
   </si>
   <si>
@@ -783,7 +839,20 @@
 No se permiten campos obligatorios vacíos.</t>
   </si>
   <si>
-    <t>La informacion de la donacion que ya se agrego antes debe aparser en pantalla ya como la donacion .</t>
+    <t>Fundacion Ezperanza/Alimentos/Monetaria/Tarjeta de Credito-Debito/50.000/234563845973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.Iniciar sesión con cualquier rol.
+2.Ingresar al apartado donaciones.
+3.Ingresar los datos requeridos para finalizar la donación.
+4.Dar clic en el botón rojo que dice confirmar y donar.
+</t>
+  </si>
+  <si>
+    <t>Mostrara un letrero de donacion exitosa</t>
+  </si>
+  <si>
+    <t>Muestra el letrero de donacion exitosa y la envia.</t>
   </si>
   <si>
     <t>TC-017</t>
@@ -815,7 +884,17 @@
 No debe afectar registros históricos críticos.</t>
   </si>
   <si>
-    <t>En la pantalla no debe apareser la donacion.</t>
+    <t>Se elimino la donacion de sofia perez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.Iniciar sesión como administrador.
+2.Ingresar al apartado de donación.
+3.En la parte derecha columna acción podemos darle a la basurita para que así se elimine la donación .
+4.Dar clic en confirmar para que así se elimine la donación.
+</t>
+  </si>
+  <si>
+    <t>En la pantalla no debe apareser la donacion después de darle clic en el botón rojo de confirmar</t>
   </si>
   <si>
     <t>La donacion efectivamente desaparese de la pantalla.</t>
@@ -840,10 +919,19 @@
 realizado.</t>
   </si>
   <si>
+    <t>En el buscador se consulto una donacion anonima.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.Iniciar sesión como administrador.
+2.Ingresar al apartado de donación.
+3.En el buscador consultar alguna donación que exista .
+</t>
+  </si>
+  <si>
     <t>La donacion debe mostrarse en pantalla.</t>
   </si>
   <si>
-    <t>En la pantalla se evidencia la donacion buscada.</t>
+    <t>En la pantalla se evidencia la donacion consultada.</t>
   </si>
   <si>
     <t>TC-020</t>
@@ -858,10 +946,19 @@
 La información debe estar disponible. Se aplican restricciones por rol si es necesario.</t>
   </si>
   <si>
+    <t>No requiere</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.Iniciar sesión como administrador.
+2.Ingresar al apartado de donación.
+3.Al ingresar al apartado de donación podemos ver todas las donaciones que existen .
+</t>
+  </si>
+  <si>
     <t>Las donaciones deben verse en pantalla.</t>
   </si>
   <si>
-    <t>Al seleccionar el apartado todas aparesen todas las donaciones.</t>
+    <t>Al seleccionar el apartado de donaciones  aparesen todas las donaciones.</t>
   </si>
   <si>
     <t>TC-021</t>
@@ -896,9 +993,21 @@
 </t>
   </si>
   <si>
+    <t>Tarjeta de credito/Debito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.Iniciar sesión como administrador.
+2.Ingresar al apartado de donación.
+3.Modificar el método de pago en la sección detalle de aportación economica .
+</t>
+  </si>
+  <si>
     <t>El metodo de pago debe verse como una serie de opciones (desplegable)</t>
   </si>
   <si>
+    <t>Los metodos de pago se evidencian como un desplegable editable.</t>
+  </si>
+  <si>
     <t>Caso de Prueba</t>
   </si>
   <si>
@@ -911,9 +1020,48 @@
     <t>.</t>
   </si>
   <si>
+    <t>Al actualizar el ususario la informacion se ve en pantalla justo en el usuario anterior.</t>
+  </si>
+  <si>
+    <t>Al eliminar usuario ya no aparese mas en pantalla y muestra menos ususarios de los que habian</t>
+  </si>
+  <si>
+    <t>Podemos notar que hay un buscador donde podemos buscar al usuario por su nombre y lo podemos ver en pantalla.</t>
+  </si>
+  <si>
+    <t>Al ingresar al apartado usuarios podemos ver de entrada a todos los ususarios seccionados en filas.</t>
+  </si>
+  <si>
     <t>Al crear el evento, no demora ma de 1 segundo para que se vea en pantalla con la informacion que se ingreso. Funciona correctamente</t>
   </si>
   <si>
+    <t>Al actualizar el evento se ve claramente la informacion proporcionada en pantalla en lugar de la anterior informacion.</t>
+  </si>
+  <si>
+    <t>El evento en custion se elimina y ya no se puede ver en pantalla.</t>
+  </si>
+  <si>
+    <t>Al consultar el evento por separado vemos que se filtra correctamente.</t>
+  </si>
+  <si>
+    <t>Vemos todos los eventos que exsiten en el aplicativo apenas ingresamos a la seccion de eventos</t>
+  </si>
+  <si>
+    <t>Al crear la donacion vemos que, sale un recuadro que nos dice que la donacion a sido exitosa y vemos que un cartel que nos lo confirma.</t>
+  </si>
+  <si>
+    <t>La donacion desaparese al instrtante depues de dar clic enconfirmar a la eliminacion de la donacion encuestion.</t>
+  </si>
+  <si>
+    <t>Al consultar una donacion en el buscador se evidencia que si hace la filtracion de la donacion requerida.</t>
+  </si>
+  <si>
+    <t>Vemos que para ver todas las donaciones no debemos hacer nada, simplemente ingresar como administrador y ingresar al apartado de donaciones.</t>
+  </si>
+  <si>
+    <t>Al modicar el metodo de pago se evidenvia que al instante se muestra el metodo de pago que haz elegido.</t>
+  </si>
+  <si>
     <t>Bug ID</t>
   </si>
   <si>
@@ -977,118 +1125,226 @@
     <t>EV-003</t>
   </si>
   <si>
+    <t>EV-003_LoginExitoso.png</t>
+  </si>
+  <si>
     <t>EV-004</t>
   </si>
   <si>
+    <t>Captura  de UpdateUser exitoso</t>
+  </si>
+  <si>
+    <t>EV-004_UpdateUserExitoso.png</t>
+  </si>
+  <si>
+    <t>EV-005</t>
+  </si>
+  <si>
+    <t>EV-005_UpdateUserExitoso.png</t>
+  </si>
+  <si>
+    <t>EV-006</t>
+  </si>
+  <si>
+    <t>EV-006_UpdateUserExitoso.png</t>
+  </si>
+  <si>
+    <t>EV-007</t>
+  </si>
+  <si>
+    <t>Captura de DeleteUser exitoso</t>
+  </si>
+  <si>
+    <t>EV-007_DeleteUserrExitoso.png</t>
+  </si>
+  <si>
+    <t>EV-008</t>
+  </si>
+  <si>
+    <t>EV-008_DeleteUserrExitoso.png</t>
+  </si>
+  <si>
+    <t>EV-009</t>
+  </si>
+  <si>
+    <t>EV-009_DeleteUserrExitoso.png</t>
+  </si>
+  <si>
+    <t>EV-010</t>
+  </si>
+  <si>
+    <t>Captura de  GetUserById exitoso</t>
+  </si>
+  <si>
+    <t>EV-0010_GetUserByIdExitoso.png</t>
+  </si>
+  <si>
+    <t>EV-011</t>
+  </si>
+  <si>
+    <t>Captura de GetUserAll exitoso</t>
+  </si>
+  <si>
+    <t>EV-0011_GetUserAllExitoso.png</t>
+  </si>
+  <si>
+    <t>EV-012</t>
+  </si>
+  <si>
+    <t>Captura de createEvent exitoso</t>
+  </si>
+  <si>
+    <t>EV-0012_CreateEventExitoso.png</t>
+  </si>
+  <si>
+    <t>EV-013</t>
+  </si>
+  <si>
+    <t>EV-0013_CreateEventExitoso.png</t>
+  </si>
+  <si>
+    <t>EV-014</t>
+  </si>
+  <si>
+    <t>EV-0014_CreateEventExitoso.png</t>
+  </si>
+  <si>
+    <t>EV-015</t>
+  </si>
+  <si>
+    <t>Captura de UpdateEvent exitoso</t>
+  </si>
+  <si>
+    <t>EV-0015_UpdateEventExitoso.png</t>
+  </si>
+  <si>
+    <t>EV-016</t>
+  </si>
+  <si>
+    <t>EV-0016_UpdateEventExitoso.png</t>
+  </si>
+  <si>
+    <t>EV-017</t>
+  </si>
+  <si>
+    <t>EV-0017_UpdateEventExitoso.png</t>
+  </si>
+  <si>
+    <t>EV-018</t>
+  </si>
+  <si>
+    <t>EV-0018_UpdateEventExitoso.png</t>
+  </si>
+  <si>
+    <t>EV-019</t>
+  </si>
+  <si>
+    <t>Captura de DeleteEvent exitoso</t>
+  </si>
+  <si>
+    <t>EV-019_DeleteEvent exitoso.png</t>
+  </si>
+  <si>
+    <t>EV-020</t>
+  </si>
+  <si>
+    <t>EV-020_DeleteEvent exitoso.png</t>
+  </si>
+  <si>
+    <t>EV-021</t>
+  </si>
+  <si>
+    <t>Captura GetEventById</t>
+  </si>
+  <si>
+    <t>EV-021_GetEventById exitoso.png</t>
+  </si>
+  <si>
+    <t>EV-022</t>
+  </si>
+  <si>
+    <t>Captura GetEventAll</t>
+  </si>
+  <si>
+    <t>EV-021_GetEventAll exitoso.png</t>
+  </si>
+  <si>
+    <t>EV-</t>
+  </si>
+  <si>
     <t xml:space="preserve">Captura </t>
   </si>
   <si>
-    <t>EV-005</t>
-  </si>
-  <si>
-    <t>EV-006</t>
-  </si>
-  <si>
-    <t>EV-007</t>
-  </si>
-  <si>
-    <t>EV-008</t>
-  </si>
-  <si>
-    <t>EV-009</t>
-  </si>
-  <si>
-    <t>EV-010</t>
-  </si>
-  <si>
-    <t>EV-011</t>
-  </si>
-  <si>
-    <t>EV-012</t>
-  </si>
-  <si>
-    <t>EV-013</t>
-  </si>
-  <si>
-    <t>EV-014</t>
-  </si>
-  <si>
-    <t>EV-015</t>
-  </si>
-  <si>
-    <t>EV-016</t>
-  </si>
-  <si>
-    <t>EV-017</t>
-  </si>
-  <si>
-    <t>EV-018</t>
-  </si>
-  <si>
-    <t>Captura de creacion de evento</t>
-  </si>
-  <si>
-    <t>EV-018_CreacionEventoExitoso.png</t>
-  </si>
-  <si>
-    <t>EV-019</t>
-  </si>
-  <si>
-    <t>EV-019_CreacionEventoExitoso.png</t>
-  </si>
-  <si>
-    <t>EV-020</t>
-  </si>
-  <si>
-    <t>EV-020_CreacionEventoExitoso.png</t>
-  </si>
-  <si>
-    <t>EV-021</t>
-  </si>
-  <si>
-    <t>EV-022</t>
-  </si>
-  <si>
     <t>EV-023</t>
   </si>
   <si>
+    <t>Captura de CreateDonation exitoso</t>
+  </si>
+  <si>
+    <t>EV-023_CreateDonation exitoso exitoso.png</t>
+  </si>
+  <si>
     <t>EV-024</t>
   </si>
   <si>
+    <t>EV-024_CreateDonation exitoso exitoso.png</t>
+  </si>
+  <si>
     <t>EV-025</t>
   </si>
   <si>
+    <t>Captura de DeleteDonation exitoso</t>
+  </si>
+  <si>
+    <t>EV-025_ DeleteDonation exitoso.png</t>
+  </si>
+  <si>
     <t>EV-026</t>
   </si>
   <si>
+    <t>EV-026_ DeleteDonation exitoso.png</t>
+  </si>
+  <si>
     <t>EV-027</t>
   </si>
   <si>
+    <t>EV-027_ DeleteDonation exitoso.png</t>
+  </si>
+  <si>
     <t>EV-028</t>
   </si>
   <si>
+    <t>EV-028_ DeleteDonation exitoso.png</t>
+  </si>
+  <si>
     <t>EV-029</t>
   </si>
   <si>
+    <t>Captura GetDonationById exitoso</t>
+  </si>
+  <si>
+    <t>EV-029_ GetDonationById exitosa exitoso.png</t>
+  </si>
+  <si>
     <t>EV-030</t>
   </si>
   <si>
+    <t>Captura GetDonationAll exitoso</t>
+  </si>
+  <si>
+    <t>EV-030_ GetDonationAll exitosa exitoso.png</t>
+  </si>
+  <si>
     <t>EV-031</t>
   </si>
   <si>
+    <t>Captura de Gestionar  metodo de pago  exitoso</t>
+  </si>
+  <si>
+    <t>EV-031_ Gestionar  metodo de pago  exitoso.png</t>
+  </si>
+  <si>
     <t>EV-032</t>
-  </si>
-  <si>
-    <t>EV-033</t>
-  </si>
-  <si>
-    <t>EV-034</t>
-  </si>
-  <si>
-    <t>EV-035</t>
-  </si>
-  <si>
-    <t>EV-036</t>
   </si>
 </sst>
 </file>
@@ -1171,7 +1427,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1195,11 +1451,8 @@
     <xf borderId="1" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
@@ -1207,10 +1460,7 @@
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
@@ -3442,22 +3692,22 @@
         <v>143</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="H3" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="H3" s="5" t="s">
         <v>145</v>
       </c>
+      <c r="I3" s="5" t="s">
+        <v>146</v>
+      </c>
       <c r="J3" s="5" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K3" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="L3" s="9" t="s">
-        <v>146</v>
+      <c r="L3" s="9">
+        <v>46199.0</v>
       </c>
       <c r="M3" s="3"/>
     </row>
@@ -3478,31 +3728,31 @@
         <v>150</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="I4" s="3" t="s">
         <v>152</v>
       </c>
+      <c r="H4" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>154</v>
+      </c>
       <c r="J4" s="5" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K4" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="L4" s="10">
-        <v>46184.0</v>
+      <c r="L4" s="9">
+        <v>46199.0</v>
       </c>
       <c r="M4" s="3"/>
     </row>
     <row r="5" ht="26.25" customHeight="1">
       <c r="A5" s="7" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>27</v>
@@ -3511,40 +3761,40 @@
         <v>26</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>160</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K5" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="L5" s="10">
-        <v>46184.0</v>
+      <c r="L5" s="9">
+        <v>46199.0</v>
       </c>
       <c r="M5" s="3"/>
     </row>
     <row r="6" ht="26.25" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>32</v>
@@ -3553,34 +3803,34 @@
         <v>34</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>168</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K6" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="L6" s="9" t="s">
-        <v>163</v>
+      <c r="L6" s="9">
+        <v>46199.0</v>
       </c>
       <c r="M6" s="3"/>
     </row>
     <row r="7" ht="26.25" customHeight="1">
       <c r="A7" s="7" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>38</v>
@@ -3588,38 +3838,38 @@
       <c r="C7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>165</v>
+      <c r="D7" s="6" t="s">
+        <v>170</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>170</v>
+        <v>174</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>175</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>11</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="L7" s="10">
-        <v>46184.0</v>
+        <v>176</v>
+      </c>
+      <c r="L7" s="9">
+        <v>46199.0</v>
       </c>
       <c r="M7" s="3"/>
     </row>
     <row r="8" ht="26.25" customHeight="1">
       <c r="A8" s="7" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>43</v>
@@ -3628,37 +3878,37 @@
         <v>42</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>143</v>
+        <v>179</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>180</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="I8" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="K8" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="J8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="L8" s="10">
-        <v>46184.0</v>
+      <c r="L8" s="9">
+        <v>46199.0</v>
       </c>
       <c r="M8" s="3"/>
     </row>
     <row r="9" ht="26.25" customHeight="1">
       <c r="A9" s="7" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>47</v>
@@ -3666,38 +3916,38 @@
       <c r="C9" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>178</v>
+      <c r="D9" s="5" t="s">
+        <v>185</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>143</v>
+        <v>186</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>187</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>143</v>
+        <v>188</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="L9" s="10">
-        <v>46185.0</v>
+        <v>176</v>
+      </c>
+      <c r="L9" s="9">
+        <v>46199.0</v>
       </c>
       <c r="M9" s="3"/>
     </row>
     <row r="10" ht="26.25" customHeight="1">
       <c r="A10" s="7" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>53</v>
@@ -3706,115 +3956,115 @@
         <v>52</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>143</v>
+        <v>192</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>194</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>143</v>
+        <v>195</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="L10" s="10">
-        <v>46185.0</v>
+        <v>176</v>
+      </c>
+      <c r="L10" s="9">
+        <v>46199.0</v>
       </c>
       <c r="M10" s="3"/>
     </row>
     <row r="11" ht="26.25" customHeight="1">
       <c r="A11" s="7" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>57</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>143</v>
+        <v>201</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>165</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>143</v>
+        <v>202</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="L11" s="10">
-        <v>46185.0</v>
+        <v>176</v>
+      </c>
+      <c r="L11" s="12" t="s">
+        <v>205</v>
       </c>
       <c r="M11" s="3"/>
     </row>
     <row r="12" ht="26.25" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>62</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>143</v>
+        <v>205</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>143</v>
+        <v>205</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="I12" s="13" t="s">
-        <v>198</v>
+        <v>210</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>205</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>18</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="L12" s="10">
-        <v>46185.0</v>
+        <v>211</v>
+      </c>
+      <c r="L12" s="12" t="s">
+        <v>205</v>
       </c>
       <c r="M12" s="3"/>
     </row>
     <row r="13" ht="26.25" customHeight="1">
       <c r="A13" s="7" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>68</v>
@@ -3823,37 +4073,37 @@
         <v>67</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>143</v>
+        <v>205</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>143</v>
+        <v>205</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>204</v>
+        <v>215</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>205</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>18</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="L13" s="10">
-        <v>46185.0</v>
+        <v>211</v>
+      </c>
+      <c r="L13" s="12" t="s">
+        <v>205</v>
       </c>
       <c r="M13" s="3"/>
     </row>
     <row r="14" ht="26.25" customHeight="1">
       <c r="A14" s="7" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>73</v>
@@ -3865,34 +4115,34 @@
         <v>74</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>143</v>
+        <v>205</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>143</v>
+        <v>205</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>207</v>
+        <v>217</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>205</v>
       </c>
       <c r="J14" s="5" t="s">
         <v>18</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="L14" s="10">
-        <v>46188.0</v>
+        <v>211</v>
+      </c>
+      <c r="L14" s="12" t="s">
+        <v>205</v>
       </c>
       <c r="M14" s="3"/>
     </row>
     <row r="15" ht="26.25" customHeight="1">
       <c r="A15" s="7" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>78</v>
@@ -3901,76 +4151,76 @@
         <v>77</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>143</v>
+        <v>205</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>143</v>
+        <v>205</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>143</v>
+        <v>205</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>18</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="L15" s="10">
-        <v>46188.0</v>
+        <v>211</v>
+      </c>
+      <c r="L15" s="12" t="s">
+        <v>205</v>
       </c>
       <c r="M15" s="3"/>
     </row>
     <row r="16" ht="26.25" customHeight="1">
       <c r="A16" s="7" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>82</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>143</v>
+        <v>205</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>143</v>
+        <v>205</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>217</v>
+        <v>226</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>205</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>18</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="L16" s="10">
-        <v>46188.0</v>
+        <v>227</v>
+      </c>
+      <c r="L16" s="12" t="s">
+        <v>205</v>
       </c>
       <c r="M16" s="3"/>
     </row>
     <row r="17" ht="26.25" customHeight="1">
       <c r="A17" s="7" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>88</v>
@@ -3979,37 +4229,37 @@
         <v>87</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>143</v>
+        <v>230</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>232</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>143</v>
+        <v>234</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="L17" s="14">
-        <v>46188.0</v>
+        <v>227</v>
+      </c>
+      <c r="L17" s="9">
+        <v>46199.0</v>
       </c>
       <c r="M17" s="3"/>
     </row>
     <row r="18" ht="26.25" customHeight="1">
       <c r="A18" s="7" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>93</v>
@@ -4018,37 +4268,37 @@
         <v>92</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>143</v>
+        <v>237</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>205</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>143</v>
+        <v>205</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>143</v>
+        <v>205</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>18</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="L18" s="14">
-        <v>46189.0</v>
+        <v>227</v>
+      </c>
+      <c r="L18" s="12" t="s">
+        <v>205</v>
       </c>
       <c r="M18" s="3"/>
     </row>
     <row r="19" ht="26.25" customHeight="1">
       <c r="A19" s="7" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>97</v>
@@ -4057,37 +4307,37 @@
         <v>96</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>230</v>
+        <v>241</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>244</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="L19" s="14">
-        <v>46189.0</v>
+        <v>246</v>
+      </c>
+      <c r="L19" s="9">
+        <v>46199.0</v>
       </c>
       <c r="M19" s="3"/>
     </row>
     <row r="20" ht="26.25" customHeight="1">
       <c r="A20" s="7" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>101</v>
@@ -4096,37 +4346,37 @@
         <v>100</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>143</v>
+        <v>249</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>237</v>
+        <v>252</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>253</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="L20" s="14">
-        <v>46190.0</v>
+        <v>246</v>
+      </c>
+      <c r="L20" s="9">
+        <v>46199.0</v>
       </c>
       <c r="M20" s="3"/>
     </row>
     <row r="21" ht="26.25" customHeight="1">
       <c r="A21" s="7" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>106</v>
@@ -4135,37 +4385,37 @@
         <v>105</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>143</v>
+        <v>256</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>258</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>242</v>
+        <v>259</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>260</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="L21" s="14">
-        <v>46190.0</v>
+        <v>246</v>
+      </c>
+      <c r="L21" s="9">
+        <v>46199.0</v>
       </c>
       <c r="M21" s="3"/>
     </row>
     <row r="22" ht="26.25" customHeight="1">
       <c r="A22" s="7" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>111</v>
@@ -4174,37 +4424,37 @@
         <v>110</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>143</v>
+        <v>205</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>143</v>
+        <v>205</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>242</v>
+        <v>259</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>205</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>18</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="L22" s="14">
-        <v>46190.0</v>
+        <v>246</v>
+      </c>
+      <c r="L22" s="12" t="s">
+        <v>205</v>
       </c>
       <c r="M22" s="3"/>
     </row>
     <row r="23" ht="21.75" customHeight="1">
       <c r="A23" s="7" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>116</v>
@@ -4213,48 +4463,48 @@
         <v>115</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>143</v>
+        <v>266</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>268</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>143</v>
+        <v>270</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="L23" s="14">
-        <v>46191.0</v>
+        <v>246</v>
+      </c>
+      <c r="L23" s="9">
+        <v>46199.0</v>
       </c>
       <c r="M23" s="3"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="15"/>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="16"/>
-      <c r="L24" s="18"/>
-      <c r="M24" s="16"/>
+      <c r="A24" s="13"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="15"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="16"/>
+      <c r="M24" s="14"/>
     </row>
     <row r="25" ht="14.25" customHeight="1"/>
     <row r="26" ht="14.25" customHeight="1"/>
@@ -5257,13 +5507,13 @@
         <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>251</v>
+        <v>272</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
@@ -5276,11 +5526,11 @@
       <c r="C2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="E2" s="20" t="s">
-        <v>253</v>
+      <c r="D2" s="17" t="s">
+        <v>273</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
@@ -5291,13 +5541,13 @@
         <v>140</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="E3" s="20" t="s">
-        <v>253</v>
+        <v>11</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>275</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
@@ -5308,13 +5558,13 @@
         <v>147</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="E4" s="20" t="s">
-        <v>253</v>
+        <v>11</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>276</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
@@ -5322,16 +5572,16 @@
         <v>26</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="E5" s="20" t="s">
-        <v>253</v>
+        <v>11</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>277</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
@@ -5339,16 +5589,16 @@
         <v>32</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="E6" s="20" t="s">
-        <v>253</v>
+        <v>11</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>278</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
@@ -5356,16 +5606,16 @@
         <v>37</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="E7" s="20" t="s">
-        <v>253</v>
+      <c r="D7" s="17" t="s">
+        <v>279</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
@@ -5373,16 +5623,16 @@
         <v>42</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>253</v>
+        <v>11</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
@@ -5390,16 +5640,16 @@
         <v>46</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>253</v>
+        <v>11</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>281</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
@@ -5407,16 +5657,16 @@
         <v>52</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="E10" s="20" t="s">
-        <v>253</v>
+        <v>11</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>282</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
@@ -5424,16 +5674,16 @@
         <v>57</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="E11" s="20" t="s">
-        <v>253</v>
+        <v>11</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>283</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
@@ -5441,16 +5691,16 @@
         <v>62</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="E12" s="20" t="s">
-        <v>253</v>
+      <c r="D12" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
@@ -5458,16 +5708,16 @@
         <v>67</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>253</v>
+      <c r="D13" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
@@ -5475,16 +5725,16 @@
         <v>72</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="E14" s="20" t="s">
-        <v>253</v>
+      <c r="D14" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
@@ -5492,16 +5742,16 @@
         <v>77</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>253</v>
+      <c r="D15" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
@@ -5509,16 +5759,16 @@
         <v>82</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="E16" s="20" t="s">
-        <v>253</v>
+      <c r="D16" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
@@ -5526,16 +5776,16 @@
         <v>87</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="E17" s="20" t="s">
-        <v>253</v>
+      <c r="D17" s="17" t="s">
+        <v>284</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
@@ -5543,16 +5793,16 @@
         <v>92</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="E18" s="20" t="s">
-        <v>253</v>
+      <c r="D18" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
@@ -5560,16 +5810,16 @@
         <v>96</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="E19" s="20" t="s">
-        <v>253</v>
+      <c r="D19" s="17" t="s">
+        <v>285</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
@@ -5577,16 +5827,16 @@
         <v>100</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="E20" s="20" t="s">
-        <v>253</v>
+      <c r="D20" s="17" t="s">
+        <v>286</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
@@ -5594,16 +5844,16 @@
         <v>105</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D21" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="E21" s="20" t="s">
-        <v>253</v>
+      <c r="D21" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
@@ -5611,16 +5861,16 @@
         <v>110</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D22" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="E22" s="20" t="s">
-        <v>253</v>
+      <c r="D22" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1">
@@ -5628,16 +5878,16 @@
         <v>115</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="E23" s="20" t="s">
-        <v>253</v>
+      <c r="D23" s="17" t="s">
+        <v>288</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1"/>
@@ -6637,16 +6887,16 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>255</v>
+        <v>289</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>256</v>
+        <v>290</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>257</v>
+        <v>291</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -6655,7 +6905,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>258</v>
+        <v>292</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>129</v>
@@ -6666,25 +6916,25 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="7" t="s">
-        <v>259</v>
+        <v>293</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>260</v>
+        <v>294</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>261</v>
+        <v>295</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>262</v>
+        <v>296</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>10</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>263</v>
+        <v>297</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>264</v>
+        <v>298</v>
       </c>
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
@@ -7859,39 +8109,39 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>265</v>
+        <v>299</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>300</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>256</v>
+        <v>290</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>268</v>
+        <v>302</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="7" t="s">
-        <v>269</v>
+        <v>303</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>131</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D2" s="19" t="s">
-        <v>271</v>
-      </c>
-      <c r="E2" s="19" t="s">
-        <v>272</v>
+        <v>304</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>305</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>306</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>139</v>
@@ -7899,19 +8149,19 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="B3" s="19" t="s">
+        <v>307</v>
+      </c>
+      <c r="B3" s="17" t="s">
         <v>131</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>271</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>274</v>
+        <v>304</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>305</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>308</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>139</v>
@@ -7919,19 +8169,19 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="B4" s="19" t="s">
+        <v>309</v>
+      </c>
+      <c r="B4" s="17" t="s">
         <v>131</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>271</v>
-      </c>
-      <c r="E4" s="19" t="s">
-        <v>274</v>
+        <v>304</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>305</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>310</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>139</v>
@@ -7939,19 +8189,19 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="B5" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="B5" s="17" t="s">
         <v>140</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>143</v>
+        <v>304</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>312</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>313</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>139</v>
@@ -7959,19 +8209,19 @@
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="B6" s="19" t="s">
+        <v>314</v>
+      </c>
+      <c r="B6" s="17" t="s">
         <v>140</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>143</v>
+        <v>304</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>312</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>315</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>139</v>
@@ -7979,19 +8229,19 @@
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="7" t="s">
-        <v>279</v>
+        <v>316</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>140</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>143</v>
+        <v>304</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>312</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>317</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>139</v>
@@ -7999,19 +8249,19 @@
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="7" t="s">
-        <v>280</v>
+        <v>318</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>147</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>143</v>
+        <v>304</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>319</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>320</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>139</v>
@@ -8019,19 +8269,19 @@
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="B9" s="19" t="s">
+        <v>321</v>
+      </c>
+      <c r="B9" s="17" t="s">
         <v>147</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>143</v>
+        <v>304</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>319</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>322</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>139</v>
@@ -8039,19 +8289,19 @@
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="7" t="s">
-        <v>282</v>
+        <v>323</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>147</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>143</v>
+        <v>304</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>319</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>324</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>139</v>
@@ -8059,19 +8309,19 @@
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="7" t="s">
-        <v>283</v>
+        <v>325</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>143</v>
+        <v>304</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>326</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>327</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>139</v>
@@ -8079,17 +8329,19 @@
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="B12" s="7"/>
+        <v>328</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>162</v>
+      </c>
       <c r="C12" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>143</v>
+        <v>304</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>329</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>330</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>139</v>
@@ -8097,503 +8349,570 @@
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>153</v>
+        <v>331</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>169</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>143</v>
+        <v>304</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>332</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>333</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>139</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>158</v>
+        <v>334</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>169</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="E14" s="19" t="s">
-        <v>143</v>
+        <v>304</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>332</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>335</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>139</v>
+        <v>176</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="B15" s="7"/>
+        <v>336</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>169</v>
+      </c>
       <c r="C15" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D15" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="E15" s="19" t="s">
-        <v>143</v>
+        <v>304</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>332</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>337</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>139</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="7" t="s">
-        <v>288</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>158</v>
+        <v>338</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>177</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="E16" s="19" t="s">
-        <v>143</v>
+        <v>304</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>339</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>340</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>139</v>
+        <v>176</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>164</v>
+        <v>341</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>177</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D17" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="E17" s="19" t="s">
-        <v>143</v>
+        <v>304</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>339</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>342</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>139</v>
+        <v>176</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="7" t="s">
-        <v>290</v>
-      </c>
-      <c r="B18" s="7"/>
+        <v>343</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>177</v>
+      </c>
       <c r="C18" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="E18" s="19" t="s">
-        <v>143</v>
+        <v>304</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>339</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>344</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>139</v>
+        <v>176</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="7" t="s">
-        <v>291</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>164</v>
+        <v>345</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>177</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D19" s="19" t="s">
-        <v>292</v>
-      </c>
-      <c r="E19" s="19" t="s">
-        <v>293</v>
+        <v>304</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>339</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>346</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>164</v>
+        <v>347</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>184</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D20" s="19" t="s">
-        <v>292</v>
-      </c>
-      <c r="E20" s="19" t="s">
-        <v>295</v>
+        <v>304</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>348</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>349</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="7" t="s">
-        <v>296</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>164</v>
+        <v>350</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>184</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D21" s="19" t="s">
-        <v>292</v>
-      </c>
-      <c r="E21" s="19" t="s">
-        <v>297</v>
+        <v>304</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>348</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>351</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>172</v>
+        <v>352</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>191</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D22" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="E22" s="19" t="s">
-        <v>143</v>
+        <v>304</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>353</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>354</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>171</v>
+        <v>211</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>177</v>
+        <v>355</v>
+      </c>
+      <c r="B23" s="17" t="s">
+        <v>198</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D23" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="E23" s="19" t="s">
-        <v>143</v>
+        <v>304</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>356</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>357</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>171</v>
+        <v>211</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1">
-      <c r="A24" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>182</v>
+      <c r="A24" s="17" t="s">
+        <v>358</v>
+      </c>
+      <c r="B24" s="17" t="s">
+        <v>206</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D24" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="E24" s="19" t="s">
-        <v>143</v>
+        <v>304</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>359</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>205</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>171</v>
+        <v>211</v>
       </c>
     </row>
     <row r="25" ht="14.25" customHeight="1">
-      <c r="A25" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>187</v>
+      <c r="A25" s="17" t="s">
+        <v>358</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>212</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D25" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="E25" s="19" t="s">
-        <v>143</v>
+        <v>304</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>359</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>205</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>171</v>
+        <v>211</v>
       </c>
     </row>
     <row r="26" ht="14.25" customHeight="1">
-      <c r="A26" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>193</v>
+      <c r="A26" s="17" t="s">
+        <v>358</v>
+      </c>
+      <c r="B26" s="17" t="s">
+        <v>216</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D26" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="E26" s="19" t="s">
-        <v>143</v>
+        <v>304</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>359</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>205</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
     </row>
     <row r="27" ht="14.25" customHeight="1">
-      <c r="A27" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>200</v>
+      <c r="A27" s="17" t="s">
+        <v>358</v>
+      </c>
+      <c r="B27" s="17" t="s">
+        <v>218</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D27" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="E27" s="19" t="s">
-        <v>143</v>
+        <v>304</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>359</v>
+      </c>
+      <c r="E27" s="17" t="s">
+        <v>205</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
     </row>
     <row r="28" ht="14.25" customHeight="1">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="17" t="s">
+        <v>358</v>
+      </c>
+      <c r="B28" s="17" t="s">
+        <v>222</v>
+      </c>
+      <c r="C28" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="D28" s="17" t="s">
+        <v>359</v>
+      </c>
+      <c r="E28" s="17" t="s">
         <v>205</v>
       </c>
-      <c r="C28" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D28" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="E28" s="19" t="s">
-        <v>143</v>
-      </c>
       <c r="F28" s="5" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
     </row>
     <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>208</v>
+      <c r="A29" s="17" t="s">
+        <v>360</v>
+      </c>
+      <c r="B29" s="17" t="s">
+        <v>228</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D29" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="E29" s="19" t="s">
-        <v>143</v>
+        <v>304</v>
+      </c>
+      <c r="D29" s="17" t="s">
+        <v>361</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>362</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
     </row>
     <row r="30" ht="14.25" customHeight="1">
-      <c r="A30" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>212</v>
+      <c r="A30" s="17" t="s">
+        <v>363</v>
+      </c>
+      <c r="B30" s="17" t="s">
+        <v>228</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D30" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="E30" s="19" t="s">
-        <v>143</v>
+        <v>304</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>361</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>364</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="31" ht="14.25" customHeight="1">
-      <c r="A31" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>219</v>
+      <c r="A31" s="17" t="s">
+        <v>358</v>
+      </c>
+      <c r="B31" s="17" t="s">
+        <v>235</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D31" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="E31" s="19" t="s">
-        <v>143</v>
+        <v>304</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>359</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>205</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
     </row>
     <row r="32" ht="14.25" customHeight="1">
-      <c r="A32" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>223</v>
+      <c r="A32" s="17" t="s">
+        <v>365</v>
+      </c>
+      <c r="B32" s="17" t="s">
+        <v>239</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D32" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="E32" s="19" t="s">
-        <v>143</v>
+        <v>304</v>
+      </c>
+      <c r="D32" s="17" t="s">
+        <v>366</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>367</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
     </row>
     <row r="33" ht="14.25" customHeight="1">
-      <c r="A33" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="B33" s="7" t="s">
+      <c r="A33" s="17" t="s">
+        <v>368</v>
+      </c>
+      <c r="B33" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="D33" s="17" t="s">
+        <v>366</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>369</v>
+      </c>
+      <c r="F33" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="C33" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D33" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="E33" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>232</v>
-      </c>
     </row>
     <row r="34" ht="14.25" customHeight="1">
-      <c r="A34" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>233</v>
+      <c r="A34" s="17" t="s">
+        <v>370</v>
+      </c>
+      <c r="B34" s="17" t="s">
+        <v>239</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D34" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="E34" s="19" t="s">
-        <v>143</v>
+        <v>304</v>
+      </c>
+      <c r="D34" s="17" t="s">
+        <v>366</v>
+      </c>
+      <c r="E34" s="17" t="s">
+        <v>371</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
     </row>
     <row r="35" ht="14.25" customHeight="1">
-      <c r="A35" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>238</v>
+      <c r="A35" s="17" t="s">
+        <v>372</v>
+      </c>
+      <c r="B35" s="17" t="s">
+        <v>239</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D35" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="E35" s="19" t="s">
-        <v>143</v>
+        <v>304</v>
+      </c>
+      <c r="D35" s="17" t="s">
+        <v>366</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>373</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
     </row>
     <row r="36" ht="14.25" customHeight="1">
-      <c r="A36" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>243</v>
+      <c r="A36" s="17" t="s">
+        <v>374</v>
+      </c>
+      <c r="B36" s="17" t="s">
+        <v>247</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D36" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="E36" s="19" t="s">
-        <v>143</v>
+        <v>304</v>
+      </c>
+      <c r="D36" s="17" t="s">
+        <v>375</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>376</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
     </row>
     <row r="37" ht="14.25" customHeight="1">
-      <c r="A37" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="B37" s="7" t="s">
+      <c r="A37" s="17" t="s">
+        <v>377</v>
+      </c>
+      <c r="B37" s="17" t="s">
+        <v>254</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="D37" s="17" t="s">
+        <v>378</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>379</v>
+      </c>
+      <c r="F37" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="C37" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D37" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="E37" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="38" ht="14.25" customHeight="1"/>
-    <row r="39" ht="14.25" customHeight="1"/>
-    <row r="40" ht="14.25" customHeight="1"/>
+    </row>
+    <row r="38" ht="14.25" customHeight="1">
+      <c r="A38" s="17" t="s">
+        <v>358</v>
+      </c>
+      <c r="B38" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="D38" s="17" t="s">
+        <v>359</v>
+      </c>
+      <c r="E38" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="39" ht="14.25" customHeight="1">
+      <c r="A39" s="17" t="s">
+        <v>380</v>
+      </c>
+      <c r="B39" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="D39" s="17" t="s">
+        <v>381</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>382</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="G39" s="18" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="40" ht="14.25" customHeight="1">
+      <c r="A40" s="17" t="s">
+        <v>383</v>
+      </c>
+      <c r="B40" s="17" t="s">
+        <v>264</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="D40" s="17" t="s">
+        <v>381</v>
+      </c>
+      <c r="E40" s="17" t="s">
+        <v>382</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="G40" s="18" t="s">
+        <v>274</v>
+      </c>
+    </row>
     <row r="41" ht="14.25" customHeight="1"/>
     <row r="42" ht="14.25" customHeight="1"/>
     <row r="43" ht="14.25" customHeight="1"/>
